--- a/Bibsam_tidskriftslistor/scifree_data_nature.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_nature.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_E826057710E94AC9E5A1B686224C190FE5BAFB83" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89164D64-E74D-49D9-A240-DAE4469E96AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3DEAB9-D4BC-453E-AD8B-781131BC895F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="132">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -398,6 +398,24 @@
   </si>
   <si>
     <t>https://www.nature.com/natcities/</t>
+  </si>
+  <si>
+    <t>3005-0693</t>
+  </si>
+  <si>
+    <t>Nature Health</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/naturehealth/</t>
+  </si>
+  <si>
+    <t>3059-4499</t>
+  </si>
+  <si>
+    <t>Nature Sensors</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/natsensors/</t>
   </si>
 </sst>
 </file>
@@ -453,16 +471,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{78817C08-B59F-4A3F-9224-A76173F606CA}" name="Table2" displayName="Table2" ref="A1:G40" totalsRowShown="0">
-  <autoFilter ref="A1:G40" xr:uid="{78817C08-B59F-4A3F-9224-A76173F606CA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC19A169-76FC-432E-8C22-166106F4BAA4}" name="Table1" displayName="Table1" ref="A1:G42" totalsRowShown="0">
+  <autoFilter ref="A1:G42" xr:uid="{BC19A169-76FC-432E-8C22-166106F4BAA4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G42">
+    <sortCondition ref="D1:D42"/>
+  </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{EA9EDE84-A787-4DB6-BECD-5293F71FB108}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{B0CA1636-9C1E-4198-B92C-2C6771D9E42B}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{E827DE2F-3046-416C-83BB-80DF28F95690}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{9433CDF6-F899-45D5-A3A3-1E2B8821913B}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{C7CCB4DF-77F8-4562-A379-E90A2424BAD4}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{7E94ABCF-8AF3-4961-9F62-8B7B6ECEBA8F}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{FA54435D-3717-4027-AEBD-34D64E7AB40D}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{82021F89-3C7D-43FC-AEE1-F82994219954}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{322DA9E2-9222-4D85-A36B-262633A77D7A}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{73903A98-8941-43E3-B91A-C400361A1DA1}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{C3A0E5CE-BF0E-4672-876D-D9627081664C}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{A9C53E63-19FF-4F03-ADD8-28FDEADE54C4}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{E8A0C00B-70A0-4472-B0A1-FCE4FE13D225}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{8755669E-7EF0-4ECB-B59A-DB9A352CE6DD}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -730,8 +751,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EDEEE9-EFAA-4C02-8809-4E891D9E441E}">
-  <dimension ref="A1:G40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B5085C2-14D4-434B-931E-9236EB069814}">
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -1191,13 +1212,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="F23" t="s">
         <v>8</v>
@@ -1211,13 +1232,13 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -1231,13 +1252,13 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
         <v>8</v>
@@ -1251,13 +1272,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
@@ -1271,13 +1292,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F27" t="s">
         <v>8</v>
@@ -1291,13 +1312,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s">
         <v>8</v>
@@ -1311,13 +1332,13 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="F29" t="s">
         <v>8</v>
@@ -1331,13 +1352,13 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
         <v>8</v>
@@ -1351,13 +1372,13 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
         <v>8</v>
@@ -1371,13 +1392,13 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s">
         <v>8</v>
@@ -1391,13 +1412,13 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s">
         <v>8</v>
@@ -1411,13 +1432,13 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F34" t="s">
         <v>8</v>
@@ -1431,13 +1452,13 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F35" t="s">
         <v>8</v>
@@ -1451,13 +1472,13 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F36" t="s">
         <v>8</v>
@@ -1471,13 +1492,13 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F37" t="s">
         <v>8</v>
@@ -1491,13 +1512,13 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="E38" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="F38" t="s">
         <v>8</v>
@@ -1511,13 +1532,13 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F39" t="s">
         <v>8</v>
@@ -1531,18 +1552,58 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
         <v>117</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D42" t="s">
         <v>114</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E42" t="s">
         <v>116</v>
       </c>
-      <c r="F40" t="s">
-        <v>8</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" t="s">
         <v>7</v>
       </c>
     </row>
